--- a/data/trans_dic/IP18A05-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP18A05-Estudios-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que su última consulta al médico fue por dispensación de recetas</t>
+          <t>Menores que su última consulta al médico fue por dispensación de recetas (tasa de respuesta: 98,7%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,81</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,41</t>
+          <t>0,0; 4,18</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,57</t>
+          <t>0,0; 8,08</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0; 15,69</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,22</t>
+          <t>0,0; 8,19</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,75</t>
+          <t>0,0; 4,87</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0; 2,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 57,06</t>
+          <t>0,0; 54,44</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,14</t>
+          <t>0,0; 4,25</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,97</t>
+          <t>0,0; 2,6</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,63</t>
+          <t>0,0; 3,51</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 33,16</t>
+          <t>0,0; 35,64</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,2; 1,76</t>
+          <t>0,23; 1,85</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,44; 2,01</t>
+          <t>0,33; 2,02</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,51; 2,46</t>
+          <t>0,47; 2,33</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,59</t>
+          <t>0,0; 6,73</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,01</t>
+          <t>0,0; 1,18</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,16; 1,55</t>
+          <t>0,16; 1,59</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,94; 3,44</t>
+          <t>0,93; 3,15</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,42; 11,24</t>
+          <t>1,32; 10,39</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,22; 1,19</t>
+          <t>0,2; 1,2</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,4; 1,44</t>
+          <t>0,4; 1,47</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,92; 2,49</t>
+          <t>0,96; 2,48</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,33; 7,19</t>
+          <t>1,57; 7,35</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,37</t>
+          <t>0,0; 2,6</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,02</t>
+          <t>0,0; 2,58</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,5</t>
+          <t>0,0; 2,52</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,51; 15,48</t>
+          <t>1,51; 17,14</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,74</t>
+          <t>0,0; 2,09</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,96; 5,38</t>
+          <t>1,22; 5,79</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,64</t>
+          <t>0,0; 3,01</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 4,66</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,31</t>
+          <t>0,0; 1,62</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,68; 3,19</t>
+          <t>0,83; 3,2</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,2; 2,02</t>
+          <t>0,22; 2,03</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,73; 8,24</t>
+          <t>0,7; 7,28</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,24; 1,45</t>
+          <t>0,22; 1,35</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,4; 1,63</t>
+          <t>0,33; 1,56</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,65; 2,18</t>
+          <t>0,59; 2,0</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,01; 7,0</t>
+          <t>0,79; 6,27</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,19; 1,36</t>
+          <t>0,19; 1,28</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,6; 1,95</t>
+          <t>0,53; 1,94</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,76; 2,46</t>
+          <t>0,83; 2,41</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,94; 9,85</t>
+          <t>1,7; 9,23</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,28; 1,12</t>
+          <t>0,29; 1,05</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,6; 1,48</t>
+          <t>0,63; 1,48</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,83; 1,89</t>
+          <t>0,87; 1,94</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2,08; 6,5</t>
+          <t>1,89; 6,48</t>
         </is>
       </c>
     </row>
@@ -1215,4 +1216,995 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que su última consulta al médico fue por dispensación de recetas (tasa de respuesta: 98,7%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Primarios</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>656</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>1221</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>1662</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>740</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>1921</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>1662</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>1396</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>1221</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>1921</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3595</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4418</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>0; 6068</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3746</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>0; 5136</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>0; 6148</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4237</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4095</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>0; 5695</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Secundarios</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>2911</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>4166</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>5012</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>1328</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>1380</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>2923</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>8052</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>3795</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>4290</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>7089</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>13064</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>5123</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>860; 6880</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>1401; 8498</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>2024; 10094</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4460</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4821</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>748; 7419</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>4038; 13740</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>1201; 9482</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>1564; 9403</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>3552; 13035</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>8307; 21509</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>2465; 11582</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Universitarios</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>793</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>790</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>1189</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>1568</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>483</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>4214</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>1472</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>1276</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>5004</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>2662</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>1568</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4016</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4020</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3848</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>415; 4718</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2930</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>1987; 9427</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>0; 5159</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4756</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>2661; 10208</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>720; 6581</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>409; 4257</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>3704</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>5612</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>7422</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>2896</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>3525</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>7877</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>9524</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>5716</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>7228</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>13489</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>16946</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>8612</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>1320; 8076</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>2190; 10369</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>3753; 12783</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>797; 6287</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>1182; 7990</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>3747; 13717</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>5530; 16171</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>2233; 12147</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>3578; 12854</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>8587; 20211</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>11414; 25473</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>4383; 15019</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP18A05-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP18A05-Estudios-trans_dic.xlsx
@@ -722,12 +722,12 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,18</t>
+          <t>0,0; 4,19</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,08</t>
+          <t>0,0; 8,02</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -737,12 +737,12 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,19</t>
+          <t>0,0; 7,71</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,87</t>
+          <t>0,0; 4,9</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -752,27 +752,27 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 54,44</t>
+          <t>0,0; 50,34</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,25</t>
+          <t>0,0; 3,58</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,6</t>
+          <t>0,0; 3,04</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,51</t>
+          <t>0,0; 3,41</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 35,64</t>
+          <t>0,0; 34,74</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,23; 1,85</t>
+          <t>0,2; 1,91</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,33; 2,02</t>
+          <t>0,33; 1,96</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,47; 2,33</t>
+          <t>0,55; 2,4</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,73</t>
+          <t>0,0; 6,2</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,18</t>
+          <t>0,0; 1,02</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,16; 1,59</t>
+          <t>0,16; 1,45</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,93; 3,15</t>
+          <t>0,93; 3,41</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,32; 10,39</t>
+          <t>1,4; 10,23</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,2; 1,2</t>
+          <t>0,2; 1,07</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,4; 1,47</t>
+          <t>0,4; 1,44</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,96; 2,48</t>
+          <t>0,84; 2,35</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,57; 7,35</t>
+          <t>1,16; 6,93</t>
         </is>
       </c>
     </row>
@@ -1002,32 +1002,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,58</t>
+          <t>0,0; 3,02</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,52</t>
+          <t>0,0; 2,69</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,51; 17,14</t>
+          <t>1,43; 15,32</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,09</t>
+          <t>0,0; 2,06</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,22; 5,79</t>
+          <t>1,22; 5,36</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,01</t>
+          <t>0,0; 2,73</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1037,22 +1037,22 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,62</t>
+          <t>0,0; 1,52</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,83; 3,2</t>
+          <t>0,71; 3,08</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,22; 2,03</t>
+          <t>0,22; 2,17</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,7; 7,28</t>
+          <t>0,72; 7,71</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,22; 1,35</t>
+          <t>0,22; 1,4</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,33; 1,56</t>
+          <t>0,41; 1,59</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,59; 2,0</t>
+          <t>0,58; 2,04</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,79; 6,27</t>
+          <t>1,15; 6,62</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,19; 1,28</t>
+          <t>0,22; 1,32</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,53; 1,94</t>
+          <t>0,58; 1,93</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,83; 2,41</t>
+          <t>0,75; 2,39</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,7; 9,23</t>
+          <t>1,81; 9,2</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,29; 1,05</t>
+          <t>0,3; 1,06</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,63; 1,48</t>
+          <t>0,62; 1,48</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,87; 1,94</t>
+          <t>0,84; 1,91</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,89; 6,48</t>
+          <t>1,85; 6,4</t>
         </is>
       </c>
     </row>
@@ -1509,12 +1509,12 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 3595</t>
+          <t>0; 3607</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 4418</t>
+          <t>0; 4385</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -1524,12 +1524,12 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 6068</t>
+          <t>0; 5711</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 3746</t>
+          <t>0; 3772</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -1539,27 +1539,27 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 5136</t>
+          <t>0; 4749</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 6148</t>
+          <t>0; 5188</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>0; 4237</t>
+          <t>0; 4960</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0; 4095</t>
+          <t>0; 3985</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0; 5695</t>
+          <t>0; 5552</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>860; 6880</t>
+          <t>730; 7105</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1401; 8498</t>
+          <t>1394; 8268</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2024; 10094</t>
+          <t>2388; 10409</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 4460</t>
+          <t>0; 4109</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 4821</t>
+          <t>0; 4161</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>748; 7419</t>
+          <t>740; 6755</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4038; 13740</t>
+          <t>4055; 14872</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1201; 9482</t>
+          <t>1279; 9331</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1564; 9403</t>
+          <t>1567; 8330</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3552; 13035</t>
+          <t>3546; 12768</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>8307; 21509</t>
+          <t>7323; 20464</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2465; 11582</t>
+          <t>1824; 10913</t>
         </is>
       </c>
     </row>
@@ -1920,37 +1920,37 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 4016</t>
+          <t>0; 4017</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 4020</t>
+          <t>0; 4713</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 3848</t>
+          <t>0; 4104</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>415; 4718</t>
+          <t>394; 4219</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 2930</t>
+          <t>0; 2876</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1987; 9427</t>
+          <t>1986; 8728</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 5159</t>
+          <t>0; 4694</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1960,22 +1960,22 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 4756</t>
+          <t>0; 4479</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2661; 10208</t>
+          <t>2256; 9825</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>720; 6581</t>
+          <t>719; 7052</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>409; 4257</t>
+          <t>420; 4504</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1320; 8076</t>
+          <t>1329; 8387</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2190; 10369</t>
+          <t>2710; 10542</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3753; 12783</t>
+          <t>3692; 13046</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>797; 6287</t>
+          <t>1150; 6645</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1182; 7990</t>
+          <t>1375; 8229</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3747; 13717</t>
+          <t>4067; 13606</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>5530; 16171</t>
+          <t>5013; 16009</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2233; 12147</t>
+          <t>2388; 12110</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3578; 12854</t>
+          <t>3714; 12914</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>8587; 20211</t>
+          <t>8503; 20311</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>11414; 25473</t>
+          <t>10957; 25045</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>4383; 15019</t>
+          <t>4295; 14847</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP18A05-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP18A05-Estudios-trans_dic.xlsx
@@ -527,13 +527,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que su última consulta al médico fue por dispensación de recetas (tasa de respuesta: 98,7%)</t>
+          <t>Menores cuya última consulta médica fue por dispensación de recetas (tasa de respuesta: 98,7%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,44 +649,44 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>2,24%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0,96%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>21,03%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>0,76%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>2,23%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>2,24%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0,96%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>20,36%</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
           <t>1,15%</t>
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>12,71%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>0,0; 8,22</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 5,75</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 4,19</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 8,02</t>
-        </is>
-      </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
+          <t>0,0; 57,42</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 7,71</t>
-        </is>
-      </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,9</t>
+          <t>0,0; 4,41</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
+          <t>0,0; 7,57</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 50,34</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,58</t>
+          <t>0,0; 4,14</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,04</t>
+          <t>0,0; 2,97</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,41</t>
+          <t>0,0; 3,63</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 34,74</t>
+          <t>0,0; 34,33</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>0,34%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>0,63%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>1,85%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>4,3%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>0,78%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>0,99%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>1,16%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>2,0%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>0,34%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>0,63%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>1,85%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,36%</t>
         </is>
       </c>
     </row>
@@ -857,47 +857,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,2; 1,91</t>
+          <t>0,0; 1,01</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,33; 1,96</t>
+          <t>0,16; 1,55</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,55; 2,4</t>
+          <t>0,94; 3,44</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,2</t>
+          <t>1,42; 12,78</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,02</t>
+          <t>0,2; 1,76</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,16; 1,45</t>
+          <t>0,44; 2,01</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,93; 3,41</t>
+          <t>0,51; 2,46</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,4; 10,23</t>
+          <t>0,0; 8,31</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,2; 1,07</t>
+          <t>0,22; 1,19</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -907,12 +907,12 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,84; 2,35</t>
+          <t>0,92; 2,49</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,16; 6,93</t>
+          <t>1,32; 7,82</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>0,35%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>2,59%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0,86%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>0,51%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>0,51%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>0,78%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>5,7%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>0,35%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>2,59%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>0,86%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,55%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,6</t>
+          <t>0,0; 1,74</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
+          <t>0,96; 5,38</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 2,64</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 3,37</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
           <t>0,0; 3,02</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 2,69</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>1,43; 15,32</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 2,06</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>1,22; 5,36</t>
-        </is>
-      </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,73</t>
+          <t>0,0; 2,5</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>1,35; 14,71</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,52</t>
+          <t>0,0; 1,31</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,71; 3,08</t>
+          <t>0,68; 3,19</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,22; 2,17</t>
+          <t>0,2; 2,02</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,72; 7,71</t>
+          <t>0,66; 7,8</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>0,57%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1,12%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1,42%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>4,53%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>0,62%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>0,85%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>1,16%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>2,89%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>0,57%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>1,12%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>1,42%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,8%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,22; 1,4</t>
+          <t>0,19; 1,36</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,41; 1,59</t>
+          <t>0,6; 1,95</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,58; 2,04</t>
+          <t>0,76; 2,46</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,15; 6,62</t>
+          <t>2,0; 10,42</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,22; 1,32</t>
+          <t>0,24; 1,45</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,58; 1,93</t>
+          <t>0,4; 1,63</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,75; 2,39</t>
+          <t>0,65; 2,18</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,81; 9,2</t>
+          <t>1,0; 7,35</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,3; 1,06</t>
+          <t>0,28; 1,12</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,62; 1,48</t>
+          <t>0,6; 1,48</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,84; 1,91</t>
+          <t>0,83; 1,89</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,85; 6,4</t>
+          <t>2,07; 6,8</t>
         </is>
       </c>
     </row>
@@ -1246,13 +1246,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que su última consulta al médico fue por dispensación de recetas (tasa de respuesta: 98,7%)</t>
+          <t>Menores cuya última consulta médica fue por dispensación de recetas (tasa de respuesta: 98,7%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1260,7 +1260,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1368,42 +1368,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1436,49 +1436,49 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>1662</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>740</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>1912</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>656</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>1221</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>1662</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>740</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>1921</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>1662</t>
-        </is>
-      </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
           <t>1396</t>
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1921</t>
+          <t>1912</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>0; 6086</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4424</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>0; 3607</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>0; 4385</t>
-        </is>
-      </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
+          <t>0; 5220</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>0; 5711</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 3772</t>
+          <t>0; 3792</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
+          <t>0; 4138</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>0; 4749</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 5188</t>
+          <t>0; 5995</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>0; 4960</t>
+          <t>0; 4840</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0; 3985</t>
+          <t>0; 4240</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0; 5552</t>
+          <t>0; 5166</t>
         </is>
       </c>
     </row>
@@ -1576,42 +1576,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1644,42 +1644,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>1380</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>2923</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>8052</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>3601</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>2911</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>4166</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>5012</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>1328</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>1380</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>2923</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>8052</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>3795</t>
+          <t>1338</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>5123</t>
+          <t>4939</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>730; 7105</t>
+          <t>0; 4128</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1394; 8268</t>
+          <t>743; 7220</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2388; 10409</t>
+          <t>4104; 14993</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 4109</t>
+          <t>1189; 10711</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 4161</t>
+          <t>735; 6551</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>740; 6755</t>
+          <t>1846; 8457</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4055; 14872</t>
+          <t>2189; 10638</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1279; 9331</t>
+          <t>0; 5253</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1567; 8330</t>
+          <t>1745; 9271</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3546; 12768</t>
+          <t>3526; 12820</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>7323; 20464</t>
+          <t>8014; 21670</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1824; 10913</t>
+          <t>1941; 11499</t>
         </is>
       </c>
     </row>
@@ -1789,37 +1789,37 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1852,42 +1852,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>483</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>4214</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>1472</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>793</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>790</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>1189</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>1568</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>483</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>4214</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>1472</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1405</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1568</t>
+          <t>1405</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 4017</t>
+          <t>0; 2433</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 4713</t>
+          <t>1566; 8764</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 4104</t>
+          <t>0; 4536</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>394; 4219</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 2876</t>
+          <t>0; 5200</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1986; 8728</t>
+          <t>0; 4709</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 4694</t>
+          <t>0; 3823</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>354; 3874</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 4479</t>
+          <t>0; 3840</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2256; 9825</t>
+          <t>2170; 10189</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>719; 7052</t>
+          <t>648; 6553</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>420; 4504</t>
+          <t>364; 4300</t>
         </is>
       </c>
     </row>
@@ -1997,37 +1997,37 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2060,42 +2060,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>3525</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>7877</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>9524</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>5513</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>3704</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>5612</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>7422</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>2896</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>3525</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>7877</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>9524</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>5716</t>
+          <t>2743</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>8612</t>
+          <t>8256</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1329; 8387</t>
+          <t>1175; 8492</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2710; 10542</t>
+          <t>4256; 13773</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3692; 13046</t>
+          <t>5075; 16503</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1150; 6645</t>
+          <t>2435; 12689</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1375; 8229</t>
+          <t>1435; 8668</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>4067; 13606</t>
+          <t>2631; 10814</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>5013; 16009</t>
+          <t>4139; 13964</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2388; 12110</t>
+          <t>952; 7018</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3714; 12914</t>
+          <t>3475; 13617</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>8503; 20311</t>
+          <t>8233; 20285</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>10957; 25045</t>
+          <t>10889; 24821</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>4295; 14847</t>
+          <t>4507; 14770</t>
         </is>
       </c>
     </row>
